--- a/haver/haver-api_PCA/tickers.xlsx
+++ b/haver/haver-api_PCA/tickers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,7 +2476,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JPSIISGM@JAPAN</t>
+          <t>JPSIISCT@JAPAN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JPSCAIC@JAPAN</t>
+          <t>JPSIISGM@JAPAN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S158VBIR@INTSRVYS</t>
+          <t>JPSCAIC@JAPAN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2527,7 +2527,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S158VCIS@INTSRVYS</t>
+          <t>S158VBIR@INTSRVYS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WRS@JAPAN</t>
+          <t>S158VCIS@INTSRVYS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JPSHX202@JAPAN</t>
+          <t>WRS@JAPAN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JPSHX224@JAPAN</t>
+          <t>JPSHX202@JAPAN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JPSIVX@JAPAN</t>
+          <t>JPSHX224@JAPAN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FLED2@JAPAN</t>
+          <t>JPSIVX@JAPAN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JAFVRN2@JAPAN</t>
+          <t>FLED2@JAPAN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JAOR2@JAPAN</t>
+          <t>JAFVRN2@JAPAN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JPNECTT3@JAPAN</t>
+          <t>JAOR2@JAPAN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2680,7 +2680,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MHFA@JAPAN</t>
+          <t>JPNECTT3@JAPAN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S158ELUR@G10</t>
+          <t>MHFA@JAPAN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S158VBIE@INTSRVYS</t>
+          <t>S158ELUR@G10</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JPNCILD@JAPAN</t>
+          <t>S158VBIE@INTSRVYS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S158VBEC@INTSRVYS</t>
+          <t>JPNCILD@JAPAN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2765,7 +2765,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S158VBEH@INTSRVYS</t>
+          <t>S158VBEC@INTSRVYS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S158VBER@INTSRVYS</t>
+          <t>S158VBEH@INTSRVYS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S158VBET@INTSRVYS</t>
+          <t>S158VBER@INTSRVYS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S158VBIC@INTSRVYS</t>
+          <t>S158VBET@INTSRVYS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2833,7 +2833,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S158VBIT@INTSRVYS</t>
+          <t>S158VBIC@INTSRVYS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2850,24 +2850,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>K24S@UK</t>
+          <t>S158VBIT@INTSRVYS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S112VPMC@INTSRVYS</t>
+          <t>ENGW@UK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UNVAA3@UK</t>
+          <t>K24S@UK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UNVAI3@UK</t>
+          <t>S112VPMC@INTSRVYS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>J5EK@UK</t>
+          <t>UNVAA3@UK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>M112VPMS@INTSRVYS</t>
+          <t>UNVAI3@UK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UCBRSS@UK</t>
+          <t>UNVAO3@UK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UCBWSA@UK</t>
+          <t>J5EK@UK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UGFCGL@UK</t>
+          <t>M112VPMS@INTSRVYS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UGFCM@UK</t>
+          <t>UCBRSS@UK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UNCREGP@UK</t>
+          <t>UCBWSA@UK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>USB3PU@UK</t>
+          <t>UGFCGL@UK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IKBE@UK</t>
+          <t>UGFCM@UK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IKBG@UK</t>
+          <t>UNCREGP@UK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>UCBIEO@UK</t>
+          <t>USB3PU@UK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>UKSPT@UK</t>
+          <t>IKBE@UK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>URSHG@UK</t>
+          <t>IKBG@UK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>URSHQ@UK</t>
+          <t>UCBIEO@UK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>URSHV@UK</t>
+          <t>UKSPT@UK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>USVTVC@UK</t>
+          <t>URSHG@UK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AP2Y@UK</t>
+          <t>URSHQ@UK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KA46@UK</t>
+          <t>URSHV@UK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3224,12 +3224,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S112ELE@G10</t>
+          <t>USVTVC@UK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S112ELUR@G10</t>
+          <t>AP2Y@UK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3258,12 +3258,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>M112VPMG@INTSRVYS</t>
+          <t>KA46@UK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>N112OL1T@INTSRVYS</t>
+          <t>S112ELE@G10</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>N112VGI@INTSRVYS</t>
+          <t>S112ELUR@G10</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>UCBITO@UK</t>
+          <t>M112VPMG@INTSRVYS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3326,15 +3326,66 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>N112OL1T@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>N112VGI@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>UCBITO@UK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>UCBIVO@UK</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>lei</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
         <is>
           <t>UK</t>
         </is>

--- a/haver/haver-api_PCA/tickers.xlsx
+++ b/haver/haver-api_PCA/tickers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1915,41 +1915,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DESD262@GERMANY</t>
+          <t>NAPMEI@USECON</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DESDK@GERMANY</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>capex</t>
-        </is>
-      </c>
+          <t>V6911351@CANADA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DESTOK@GERMANY</t>
+          <t>DESD262@GERMANY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1966,7 +1962,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DESVHBK@GERMANY</t>
+          <t>DESDK@GERMANY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1983,7 +1979,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DESVUBK@GERMANY</t>
+          <t>DESTOK@GERMANY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2000,12 +1996,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DENVCCB@GERMANY</t>
+          <t>DESVHBK@GERMANY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2017,12 +2013,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DESTU47@GERMANY</t>
+          <t>DESVUBK@GERMANY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2034,7 +2030,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DESVCC@GERMANY</t>
+          <t>DENVCCB@GERMANY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2047,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DESVCONI@GERMANY</t>
+          <t>DESTU47@GERMANY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2064,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>H134VCC@G10</t>
+          <t>DESVCC@GERMANY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,12 +2081,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DESIBT@GERMANY</t>
+          <t>DESVCONI@GERMANY</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2102,12 +2098,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DESTLC@GERMANY</t>
+          <t>H134VCC@G10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,7 +2115,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DESTLGC@GERMANY</t>
+          <t>DESIBT@GERMANY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2136,7 +2132,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DESTLGD@GERMANY</t>
+          <t>DESTLC@GERMANY</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2153,7 +2149,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DESTLK@GERMANY</t>
+          <t>DESTLGC@GERMANY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2170,7 +2166,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DESVXIM@GERMANY</t>
+          <t>DESTLGD@GERMANY</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2187,7 +2183,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>E134IEX@EUDATA</t>
+          <t>DESTLK@GERMANY</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2204,7 +2200,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>E134IO@EUDATA</t>
+          <t>DESVXIM@GERMANY</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2221,12 +2217,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DENHPNRL@GERMANY</t>
+          <t>E134IEX@EUDATA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2238,12 +2234,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DESRTH@GERMANY</t>
+          <t>E134IO@EUDATA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2255,7 +2251,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DESTOR2C@GERMANY</t>
+          <t>DENHPNRL@GERMANY</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2272,12 +2268,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DENVIAB@GERMANY</t>
+          <t>DESRTH@GERMANY</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2285,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DESE250U@GERMANY</t>
+          <t>DESTOR2C@GERMANY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,7 +2302,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DESELE@GERMANY</t>
+          <t>DENVIAB@GERMANY</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2323,7 +2319,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DESVIE@GERMANY</t>
+          <t>DESE250U@GERMANY</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2340,7 +2336,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S134ELUR@G10</t>
+          <t>DESELE@GERMANY</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2357,12 +2353,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DENVZCG@GERMANY</t>
+          <t>DESVIE@GERMANY</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2374,12 +2370,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DENVZEW@GERMANY</t>
+          <t>S134ELUR@G10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2391,7 +2387,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DESVBBA@GERMANY</t>
+          <t>DENVZCG@GERMANY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2408,7 +2404,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DESVEBA@GERMANY</t>
+          <t>DENVZEW@GERMANY</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2425,7 +2421,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S134VI@INTSRVYS</t>
+          <t>DESVBBA@GERMANY</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2442,41 +2438,41 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JPSIIPBO@JAPAN</t>
+          <t>DESVEBA@GERMANY</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JPSIISBO@JAPAN</t>
+          <t>S134VI@INTSRVYS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JPSIISCT@JAPAN</t>
+          <t>JPSIIPBO@JAPAN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2493,7 +2489,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JPSIISGM@JAPAN</t>
+          <t>JPSIISBO@JAPAN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2510,12 +2506,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JPSCAIC@JAPAN</t>
+          <t>JPSIISCT@JAPAN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2523,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S158VBIR@INTSRVYS</t>
+          <t>JPSIISGM@JAPAN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,7 +2540,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S158VCIS@INTSRVYS</t>
+          <t>JPSCAIC@JAPAN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2561,7 +2557,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WRS@JAPAN</t>
+          <t>S158VBIR@INTSRVYS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2578,12 +2574,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JPSHX202@JAPAN</t>
+          <t>S158VCIS@INTSRVYS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,12 +2591,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JPSHX224@JAPAN</t>
+          <t>WRS@JAPAN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2612,7 +2608,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JPSIVX@JAPAN</t>
+          <t>JPSHX202@JAPAN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2629,12 +2625,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FLED2@JAPAN</t>
+          <t>JPSHX224@JAPAN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,12 +2642,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JAFVRN2@JAPAN</t>
+          <t>JPSIVX@JAPAN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,7 +2659,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JAOR2@JAPAN</t>
+          <t>FLED2@JAPAN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2680,7 +2676,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JPNECTT3@JAPAN</t>
+          <t>JAFVRN2@JAPAN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2697,7 +2693,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MHFA@JAPAN</t>
+          <t>JAOR2@JAPAN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2714,7 +2710,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S158ELUR@G10</t>
+          <t>JPNECTT3@JAPAN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2731,7 +2727,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S158VBIE@INTSRVYS</t>
+          <t>MHFA@JAPAN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2748,12 +2744,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JPNCILD@JAPAN</t>
+          <t>S158ELUR@G10</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2765,12 +2761,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S158VBEC@INTSRVYS</t>
+          <t>S158VBIE@INTSRVYS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,7 +2778,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S158VBEH@INTSRVYS</t>
+          <t>JPNCILD@JAPAN</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2799,7 +2795,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S158VBER@INTSRVYS</t>
+          <t>S158VBEC@INTSRVYS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,7 +2812,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S158VBET@INTSRVYS</t>
+          <t>S158VBEH@INTSRVYS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2833,7 +2829,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S158VBIC@INTSRVYS</t>
+          <t>S158VBER@INTSRVYS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2850,7 +2846,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S158VBIT@INTSRVYS</t>
+          <t>S158VBET@INTSRVYS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2867,41 +2863,41 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ENGW@UK</t>
+          <t>S158VBIC@INTSRVYS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>K24S@UK</t>
+          <t>S158VBIT@INTSRVYS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S112VPMC@INTSRVYS</t>
+          <t>ENGW@UK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2918,7 +2914,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>UNVAA3@UK</t>
+          <t>K24S@UK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2935,7 +2931,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>UNVAI3@UK</t>
+          <t>S112VPMC@INTSRVYS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,7 +2948,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UNVAO3@UK</t>
+          <t>UNVAA3@UK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2969,12 +2965,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>J5EK@UK</t>
+          <t>UNVAI3@UK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2982,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>M112VPMS@INTSRVYS</t>
+          <t>UNVAO3@UK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,7 +2999,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UCBRSS@UK</t>
+          <t>J5EK@UK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,7 +3016,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UCBWSA@UK</t>
+          <t>M112VPMS@INTSRVYS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3037,7 +3033,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>UGFCGL@UK</t>
+          <t>UCBRSS@UK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3054,7 +3050,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>UGFCM@UK</t>
+          <t>UCBWSA@UK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3071,7 +3067,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>UNCREGP@UK</t>
+          <t>UGFCGL@UK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3088,7 +3084,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>USB3PU@UK</t>
+          <t>UGFCM@UK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3105,12 +3101,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IKBE@UK</t>
+          <t>UNCREGP@UK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3118,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IKBG@UK</t>
+          <t>USB3PU@UK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,7 +3135,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>UCBIEO@UK</t>
+          <t>IKBE@UK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,12 +3152,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>UKSPT@UK</t>
+          <t>IKBG@UK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3173,12 +3169,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>URSHG@UK</t>
+          <t>UCBIEO@UK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>export</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,7 +3186,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>URSHQ@UK</t>
+          <t>UKSPT@UK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3207,7 +3203,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>URSHV@UK</t>
+          <t>URSHG@UK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3224,7 +3220,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>USVTVC@UK</t>
+          <t>URSHQ@UK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3241,12 +3237,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AP2Y@UK</t>
+          <t>URSHV@UK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3258,12 +3254,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KA46@UK</t>
+          <t>USVTVC@UK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3275,7 +3271,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S112ELE@G10</t>
+          <t>AP2Y@UK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3292,7 +3288,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S112ELUR@G10</t>
+          <t>KA46@UK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3309,12 +3305,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>M112VPMG@INTSRVYS</t>
+          <t>S112ELE@G10</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3326,12 +3322,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>N112OL1T@INTSRVYS</t>
+          <t>S112ELUR@G10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3343,7 +3339,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>N112VGI@INTSRVYS</t>
+          <t>M112VPMG@INTSRVYS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3360,7 +3356,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>UCBITO@UK</t>
+          <t>N112OL1T@INTSRVYS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3377,17 +3373,136 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>N112VGI@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>UCBITO@UK</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
           <t>UCBIVO@UK</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>lei</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>S134VPMM@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>S158VPMM@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>S112VPMM@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>S156VPMM@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>S193VPMM@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>lei</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AU</t>
         </is>
       </c>
     </row>
